--- a/3-能力管理/运行记录类文件/030204-2025年1-8月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/030204-2025年1-8月运维服务能力改进计划及跟踪.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>2025年1-8月运维服务能力改进计划及跟踪</t>
   </si>
@@ -42,9 +42,6 @@
   </si>
   <si>
     <t>改进结果跟踪</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
   <si>
     <t>待改进过程/活动</t>
@@ -1102,7 +1099,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="20.8888888888889" customWidth="1"/>
@@ -1113,10 +1110,9 @@
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="12.3796296296296" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
-    <col min="11" max="11" width="10.8796296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="41.25" customHeight="1" spans="1:11">
+    <row r="1" ht="41.25" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1129,9 +1125,8 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
     </row>
-    <row r="2" ht="26.25" customHeight="1" spans="1:11">
+    <row r="2" ht="26.25" customHeight="1" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1150,86 +1145,79 @@
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="3" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="3" ht="26.25" customHeight="1" spans="1:11">
+    <row r="3" ht="26.25" customHeight="1" spans="1:10">
       <c r="A3" s="3"/>
       <c r="B3" s="8"/>
       <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="3"/>
     </row>
-    <row r="4" ht="130" customHeight="1" spans="1:11">
+    <row r="4" ht="130" customHeight="1" spans="1:10">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="3"/>
     </row>
     <row r="5" spans="4:7">
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
-      <c r="F5"/>
       <c r="G5" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:K1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="87" orientation="landscape"/>
